--- a/project docs/GoPro_settings_list.xlsx
+++ b/project docs/GoPro_settings_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PythonProjects\Go2Kin\project docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F940FD39-685A-4152-9B19-05610D830DD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A441B9AD-2FFE-4340-9CC4-071AB3ED6BB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12960" yWindow="105" windowWidth="38700" windowHeight="15345" xr2:uid="{25ADDBA5-24B8-4C9A-8BD6-A7499FF0E2B5}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="67">
   <si>
     <t>GoPro seettings list (Hero 12 black)</t>
   </si>
@@ -235,6 +235,9 @@
   </si>
   <si>
     <t>set to Linear (4) - just for precaution as we do not use Webcam mode</t>
+  </si>
+  <si>
+    <t>YES</t>
   </si>
 </sst>
 </file>
@@ -650,6 +653,9 @@
       <c r="C6" s="2" t="s">
         <v>44</v>
       </c>
+      <c r="F6" s="2" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="7" spans="1:7" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
@@ -756,6 +762,9 @@
       <c r="E14" s="2" t="s">
         <v>44</v>
       </c>
+      <c r="F14" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="G14" s="2" t="s">
         <v>48</v>
       </c>
@@ -770,6 +779,9 @@
       <c r="D15" s="2" t="s">
         <v>44</v>
       </c>
+      <c r="F15" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="G15" s="2" t="s">
         <v>51</v>
       </c>
@@ -854,6 +866,9 @@
       <c r="D21" s="2" t="s">
         <v>44</v>
       </c>
+      <c r="F21" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="G21" s="2" t="s">
         <v>55</v>
       </c>
@@ -1064,6 +1079,9 @@
       <c r="D36" s="2" t="s">
         <v>44</v>
       </c>
+      <c r="F36" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="G36" s="2" t="s">
         <v>62</v>
       </c>
@@ -1078,6 +1096,9 @@
       <c r="D37" s="2" t="s">
         <v>44</v>
       </c>
+      <c r="F37" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="G37" s="2" t="s">
         <v>63</v>
       </c>
@@ -1119,6 +1140,9 @@
       </c>
       <c r="D40" s="2" t="s">
         <v>44</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>64</v>

--- a/project docs/GoPro_settings_list.xlsx
+++ b/project docs/GoPro_settings_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PythonProjects\Go2Kin\project docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A441B9AD-2FFE-4340-9CC4-071AB3ED6BB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB55044-A5AE-4B8A-A01D-DAFA7068AD66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12960" yWindow="105" windowWidth="38700" windowHeight="15345" xr2:uid="{25ADDBA5-24B8-4C9A-8BD6-A7499FF0E2B5}"/>
+    <workbookView xWindow="28455" yWindow="165" windowWidth="23115" windowHeight="20565" xr2:uid="{25ADDBA5-24B8-4C9A-8BD6-A7499FF0E2B5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="69">
   <si>
     <t>GoPro seettings list (Hero 12 black)</t>
   </si>
@@ -238,6 +238,12 @@
   </si>
   <si>
     <t>YES</t>
+  </si>
+  <si>
+    <t>Digital Zoom</t>
+  </si>
+  <si>
+    <t>0-100% user controlled, different API endpoint</t>
   </si>
 </sst>
 </file>
@@ -253,12 +259,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -273,10 +291,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -593,7 +622,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D861172-E68E-4083-B06D-32808119912D}">
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.42578125" customWidth="1"/>
@@ -644,508 +673,634 @@
       </c>
     </row>
     <row r="6" spans="1:7" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+      <c r="A6" s="4">
         <v>2</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F6" s="2" t="s">
+      <c r="C6" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="3" t="s">
         <v>66</v>
       </c>
+      <c r="G6" s="4"/>
     </row>
     <row r="7" spans="1:7" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+      <c r="A7" s="4">
         <v>3</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>44</v>
-      </c>
+      <c r="C7" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:7" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+      <c r="A8" s="4">
         <v>5</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G8" s="2" t="s">
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
+      <c r="A9" s="4">
         <v>30</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G9" s="2" t="s">
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
+      <c r="A10" s="4">
         <v>32</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G10" s="2" t="s">
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
+      <c r="A11" s="4">
         <v>43</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G11" s="2" t="s">
+      <c r="C11" s="4"/>
+      <c r="D11" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
+      <c r="A12" s="4">
         <v>59</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G12" s="2" t="s">
+      <c r="C12" s="4"/>
+      <c r="D12" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
+      <c r="A13" s="4">
         <v>88</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G13" s="2" t="s">
+      <c r="C13" s="4"/>
+      <c r="D13" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
+      <c r="A14" s="4">
         <v>108</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F14" s="2" t="s">
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="4" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
+      <c r="A15" s="4">
         <v>121</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F15" s="2" t="s">
+      <c r="C15" s="4"/>
+      <c r="D15" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="4" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
+      <c r="A16" s="4">
         <v>122</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G16" s="2" t="s">
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
+      <c r="A17" s="4">
         <v>123</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G17" s="2" t="s">
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:7" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
+      <c r="A18" s="4">
         <v>125</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G18" s="2" t="s">
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
+      <c r="A19" s="4">
         <v>128</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G19" s="2" t="s">
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:7" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
+      <c r="A20" s="4">
         <v>134</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G20" s="2" t="s">
+      <c r="C20" s="4"/>
+      <c r="D20" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:7" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
+      <c r="A21" s="4">
         <v>135</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F21" s="2" t="s">
+      <c r="C21" s="4"/>
+      <c r="D21" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21" s="4"/>
+      <c r="F21" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="G21" s="4" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
+      <c r="A22" s="4">
         <v>156</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G22" s="2" t="s">
+      <c r="C22" s="4"/>
+      <c r="D22" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:7" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
+      <c r="A23" s="4">
         <v>157</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G23" s="2" t="s">
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="24" spans="1:7" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
+      <c r="A24" s="4">
         <v>167</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G24" s="2" t="s">
+      <c r="C24" s="4"/>
+      <c r="D24" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:7" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
+      <c r="A25" s="4">
         <v>171</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G25" s="2" t="s">
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="26" spans="1:7" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
+      <c r="A26" s="4">
         <v>172</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G26" s="2" t="s">
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="27" spans="1:7" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
+      <c r="A27" s="4">
         <v>175</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G27" s="2" t="s">
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="28" spans="1:7" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
+      <c r="A28" s="4">
         <v>176</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G28" s="2" t="s">
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="29" spans="1:7" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
+      <c r="A29" s="4">
         <v>178</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G29" s="2" t="s">
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="30" spans="1:7" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
+      <c r="A30" s="4">
         <v>179</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G30" s="2" t="s">
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:7" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
+      <c r="A31" s="4">
         <v>182</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G31" s="2" t="s">
+      <c r="C31" s="4"/>
+      <c r="D31" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="32" spans="1:7" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
+      <c r="A32" s="4">
         <v>183</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D32" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G32" s="2" t="s">
+      <c r="C32" s="4"/>
+      <c r="D32" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="33" spans="1:7" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
+      <c r="A33" s="4">
         <v>184</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D33" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G33" s="2" t="s">
+      <c r="C33" s="4"/>
+      <c r="D33" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="34" spans="1:7" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
+      <c r="A34" s="4">
         <v>186</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E34" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G34" s="2" t="s">
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="35" spans="1:7" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
+      <c r="A35" s="4">
         <v>187</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E35" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G35" s="2" t="s">
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="36" spans="1:7" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="2">
+      <c r="A36" s="4">
         <v>189</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D36" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F36" s="2" t="s">
+      <c r="C36" s="4"/>
+      <c r="D36" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E36" s="4"/>
+      <c r="F36" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G36" s="2" t="s">
+      <c r="G36" s="4" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="37" spans="1:7" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="2">
+      <c r="A37" s="4">
         <v>190</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D37" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F37" s="2" t="s">
+      <c r="C37" s="4"/>
+      <c r="D37" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E37" s="4"/>
+      <c r="F37" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G37" s="2" t="s">
+      <c r="G37" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="38" spans="1:7" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="2">
+      <c r="A38" s="4">
         <v>191</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G38" s="2" t="s">
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="39" spans="1:7" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="2">
+      <c r="A39" s="4">
         <v>192</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E39" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G39" s="2" t="s">
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="40" spans="1:7" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
+      <c r="A40" s="4">
         <v>193</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D40" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F40" s="2" t="s">
+      <c r="C40" s="4"/>
+      <c r="D40" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E40" s="4"/>
+      <c r="F40" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G40" s="2" t="s">
+      <c r="G40" s="4" t="s">
         <v>64</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="5"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="6"/>
+    </row>
+    <row r="42" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="4"/>
+      <c r="B42" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
